--- a/output/yearly_benthic_cover_iteration_71_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_71_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.38736605278779</v>
+        <v>45.27324151277522</v>
       </c>
       <c r="M2" t="n">
-        <v>100.1744042407399</v>
+        <v>99.15023831473638</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.06080082277353</v>
+        <v>88.04405220693907</v>
       </c>
       <c r="C3" t="n">
-        <v>45.93411050195396</v>
+        <v>45.92866480198004</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228812386049873</v>
+        <v>2.228773572864342</v>
       </c>
       <c r="E3" t="n">
-        <v>5.711314790744735</v>
+        <v>5.707279550009739</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429374620166244</v>
+        <v>0.7429245242881142</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97464970657983</v>
+        <v>33.97293666433689</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17512325276471</v>
+        <v>34.17452811725325</v>
       </c>
       <c r="I3" t="n">
-        <v>6.584604087013854</v>
+        <v>6.574331501386028</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643359137603902</v>
+        <v>4.643278276800713</v>
       </c>
       <c r="K3" t="n">
-        <v>11.93919917722648</v>
+        <v>11.95594779306093</v>
       </c>
       <c r="L3" t="n">
-        <v>48.89034547176087</v>
+        <v>48.87940716608938</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7636551509413</v>
+        <v>106.7640197611303</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.27039573055625</v>
+        <v>86.99870552726782</v>
       </c>
       <c r="C4" t="n">
-        <v>42.78183759859238</v>
+        <v>42.51966922924255</v>
       </c>
       <c r="D4" t="n">
-        <v>2.191375500652386</v>
+        <v>2.1777520548744</v>
       </c>
       <c r="E4" t="n">
-        <v>6.531832141935273</v>
+        <v>6.49164973169154</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444978178551218</v>
+        <v>0.744487288995282</v>
       </c>
       <c r="G4" t="n">
-        <v>33.40398477513658</v>
+        <v>33.19522159256179</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24689962133559</v>
+        <v>34.24641529378297</v>
       </c>
       <c r="I4" t="n">
-        <v>5.498694512046781</v>
+        <v>5.490134009141311</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653111361594511</v>
+        <v>4.653045556220512</v>
       </c>
       <c r="K4" t="n">
-        <v>12.72960426944375</v>
+        <v>13.00129447273219</v>
       </c>
       <c r="L4" t="n">
-        <v>44.30565246288016</v>
+        <v>44.29641597854231</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81709433091629</v>
+        <v>99.81737968051706</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.16955528328505</v>
+        <v>85.85258863419318</v>
       </c>
       <c r="C5" t="n">
-        <v>42.53455735942577</v>
+        <v>42.22551238742913</v>
       </c>
       <c r="D5" t="n">
-        <v>2.137901477175128</v>
+        <v>2.121901530784802</v>
       </c>
       <c r="E5" t="n">
-        <v>7.137505839588773</v>
+        <v>7.089040713994239</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458198352497746</v>
+        <v>0.7458121077865926</v>
       </c>
       <c r="G5" t="n">
-        <v>32.58885954189022</v>
+        <v>32.34389854177407</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30771242148962</v>
+        <v>34.30735695818326</v>
       </c>
       <c r="I5" t="n">
-        <v>4.590382197580447</v>
+        <v>4.583253108004022</v>
       </c>
       <c r="J5" t="n">
-        <v>4.66137397031109</v>
+        <v>4.661325673666203</v>
       </c>
       <c r="K5" t="n">
-        <v>13.83044471671495</v>
+        <v>14.14741136580681</v>
       </c>
       <c r="L5" t="n">
-        <v>43.48225640963575</v>
+        <v>43.47457252428791</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84725848577646</v>
+        <v>99.84749627752385</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.88200772585841</v>
+        <v>84.42243948925942</v>
       </c>
       <c r="C6" t="n">
-        <v>41.96009221947455</v>
+        <v>41.50706668107317</v>
       </c>
       <c r="D6" t="n">
-        <v>2.075267190405255</v>
+        <v>2.051968737961364</v>
       </c>
       <c r="E6" t="n">
-        <v>7.566909968673578</v>
+        <v>7.492927254404268</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469418989786432</v>
+        <v>0.7469385224661796</v>
       </c>
       <c r="G6" t="n">
-        <v>31.63410087043502</v>
+        <v>31.27792110455172</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35932735301757</v>
+        <v>34.35917203344426</v>
       </c>
       <c r="I6" t="n">
-        <v>3.831073575731833</v>
+        <v>3.825146071018005</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668386868616519</v>
+        <v>4.668365765413622</v>
       </c>
       <c r="K6" t="n">
-        <v>15.11799227414158</v>
+        <v>15.57756051074058</v>
       </c>
       <c r="L6" t="n">
-        <v>42.79440488978442</v>
+        <v>42.78806022185281</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87248938340056</v>
+        <v>99.87268741366655</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.32812131174146</v>
+        <v>82.74408379125718</v>
       </c>
       <c r="C7" t="n">
-        <v>41.00142706656051</v>
+        <v>40.42267020902269</v>
       </c>
       <c r="D7" t="n">
-        <v>1.999695519228941</v>
+        <v>1.970135692287126</v>
       </c>
       <c r="E7" t="n">
-        <v>7.824131925395451</v>
+        <v>7.726060755661696</v>
       </c>
       <c r="F7" t="n">
-        <v>0.747897041581787</v>
+        <v>0.7478989209784824</v>
       </c>
       <c r="G7" t="n">
-        <v>30.48213264196222</v>
+        <v>30.03054949552469</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40326391276218</v>
+        <v>34.40335036501019</v>
       </c>
       <c r="I7" t="n">
-        <v>3.196643760924704</v>
+        <v>3.191720305679487</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674356509886168</v>
+        <v>4.674368256115515</v>
       </c>
       <c r="K7" t="n">
-        <v>16.67187868825854</v>
+        <v>17.25591620874281</v>
       </c>
       <c r="L7" t="n">
-        <v>42.22027553474395</v>
+        <v>42.21515952470622</v>
       </c>
       <c r="M7" t="n">
-        <v>99.893581289563</v>
+        <v>99.89374594247172</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.06089855653705</v>
+        <v>87.4002970753122</v>
       </c>
       <c r="C8" t="n">
-        <v>43.23259720125327</v>
+        <v>42.62618197268739</v>
       </c>
       <c r="D8" t="n">
-        <v>2.003916896552342</v>
+        <v>1.974286530339255</v>
       </c>
       <c r="E8" t="n">
-        <v>9.606037425339158</v>
+        <v>9.486621848083969</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494758597474592</v>
+        <v>0.7494746537122721</v>
       </c>
       <c r="G8" t="n">
-        <v>30.96443146647743</v>
+        <v>30.5056071597735</v>
       </c>
       <c r="H8" t="n">
-        <v>34.4758895483831</v>
+        <v>34.47583407076451</v>
       </c>
       <c r="I8" t="n">
-        <v>5.576923236615938</v>
+        <v>5.524256226936978</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684224123421619</v>
+        <v>4.6842165857017</v>
       </c>
       <c r="K8" t="n">
-        <v>11.93910144346296</v>
+        <v>12.59970292468783</v>
       </c>
       <c r="L8" t="n">
-        <v>44.64279551874714</v>
+        <v>44.59036037741513</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81449416346337</v>
+        <v>99.81624527479033</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.02527455021387</v>
+        <v>85.02069588882368</v>
       </c>
       <c r="C9" t="n">
-        <v>42.06281031354541</v>
+        <v>41.10364681471729</v>
       </c>
       <c r="D9" t="n">
-        <v>1.911545232261554</v>
+        <v>1.865707155685818</v>
       </c>
       <c r="E9" t="n">
-        <v>9.939211826172659</v>
+        <v>9.73353344074547</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508279526442192</v>
+        <v>0.7508298061871546</v>
       </c>
       <c r="G9" t="n">
-        <v>29.53710876996368</v>
+        <v>28.82789741606044</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53808582163406</v>
+        <v>34.53817108460911</v>
       </c>
       <c r="I9" t="n">
-        <v>4.65582024351131</v>
+        <v>4.611870696865965</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692674704026369</v>
+        <v>4.692686288669716</v>
       </c>
       <c r="K9" t="n">
-        <v>13.97472544978616</v>
+        <v>14.97930411117633</v>
       </c>
       <c r="L9" t="n">
-        <v>43.80754970231801</v>
+        <v>43.76359751224702</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84508546564956</v>
+        <v>99.84654843814064</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.75681952170297</v>
+        <v>82.49253334311905</v>
       </c>
       <c r="C10" t="n">
-        <v>40.51688045301891</v>
+        <v>39.29034286976118</v>
       </c>
       <c r="D10" t="n">
-        <v>1.809568222041429</v>
+        <v>1.751753184182062</v>
       </c>
       <c r="E10" t="n">
-        <v>10.05661701844261</v>
+        <v>9.78056094131434</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519890939321173</v>
+        <v>0.7519976276460941</v>
       </c>
       <c r="G10" t="n">
-        <v>27.9613647111407</v>
+        <v>27.06714231006665</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59149832087738</v>
+        <v>34.59189087172033</v>
       </c>
       <c r="I10" t="n">
-        <v>3.885850318192994</v>
+        <v>3.84920323540147</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699931837075733</v>
+        <v>4.699985172788089</v>
       </c>
       <c r="K10" t="n">
-        <v>16.24318047829703</v>
+        <v>17.50746665688097</v>
       </c>
       <c r="L10" t="n">
-        <v>43.11061072858652</v>
+        <v>43.07408295400046</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87067165990247</v>
+        <v>99.87189248064261</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.44164270949767</v>
+        <v>79.84833466588474</v>
       </c>
       <c r="C11" t="n">
-        <v>38.80406366643391</v>
+        <v>37.24186694644727</v>
       </c>
       <c r="D11" t="n">
-        <v>1.706639889526098</v>
+        <v>1.633939878853583</v>
       </c>
       <c r="E11" t="n">
-        <v>10.02501381720918</v>
+        <v>9.658102490689224</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529870802024272</v>
+        <v>0.7530059534665693</v>
       </c>
       <c r="G11" t="n">
-        <v>26.37092086408643</v>
+        <v>25.24675486613902</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63740568931163</v>
+        <v>34.63827385946219</v>
       </c>
       <c r="I11" t="n">
-        <v>3.242506117896735</v>
+        <v>3.211970408108088</v>
       </c>
       <c r="J11" t="n">
-        <v>4.70616925126517</v>
+        <v>4.706287209166058</v>
       </c>
       <c r="K11" t="n">
-        <v>18.55835729050235</v>
+        <v>20.15166533411526</v>
       </c>
       <c r="L11" t="n">
-        <v>42.52963875644727</v>
+        <v>42.49954540734298</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89205971338352</v>
+        <v>99.89307768790552</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.94205699133018</v>
+        <v>77.28944741642094</v>
       </c>
       <c r="C12" t="n">
-        <v>36.80632400478675</v>
+        <v>35.17902294081074</v>
       </c>
       <c r="D12" t="n">
-        <v>1.596503311577581</v>
+        <v>1.521267824119819</v>
       </c>
       <c r="E12" t="n">
-        <v>9.828920422118955</v>
+        <v>9.438728556726955</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538471885929394</v>
+        <v>0.7538762131667434</v>
       </c>
       <c r="G12" t="n">
-        <v>24.66909554103709</v>
+        <v>23.50580724441662</v>
       </c>
       <c r="H12" t="n">
-        <v>34.6769706752752</v>
+        <v>34.67830580567019</v>
       </c>
       <c r="I12" t="n">
-        <v>2.705174924022533</v>
+        <v>2.679735440028483</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711544928705871</v>
+        <v>4.711726332292146</v>
       </c>
       <c r="K12" t="n">
-        <v>21.05794300866984</v>
+        <v>22.71055258357905</v>
       </c>
       <c r="L12" t="n">
-        <v>42.04566337215742</v>
+        <v>42.02120307538498</v>
       </c>
       <c r="M12" t="n">
-        <v>99.909930385614</v>
+        <v>99.91077859977477</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.50308825105915</v>
+        <v>74.75555557727031</v>
       </c>
       <c r="C13" t="n">
-        <v>34.78511646250313</v>
+        <v>33.05797347706122</v>
       </c>
       <c r="D13" t="n">
-        <v>1.490088449162755</v>
+        <v>1.410830536686209</v>
       </c>
       <c r="E13" t="n">
-        <v>9.549862281689302</v>
+        <v>9.126075232048576</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545883691055789</v>
+        <v>0.7546276260654521</v>
       </c>
       <c r="G13" t="n">
-        <v>23.0247779947718</v>
+        <v>21.79939003776029</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71106497885661</v>
+        <v>34.71287079901079</v>
       </c>
       <c r="I13" t="n">
-        <v>2.256528870563232</v>
+        <v>2.235338682789911</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716177306909868</v>
+        <v>4.716422662909076</v>
       </c>
       <c r="K13" t="n">
-        <v>23.49691174894084</v>
+        <v>25.2444444227297</v>
       </c>
       <c r="L13" t="n">
-        <v>41.64282804066652</v>
+        <v>41.62314500465274</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92485625211049</v>
+        <v>99.92556290444365</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.38595232337053</v>
+        <v>82.34007685908233</v>
       </c>
       <c r="C14" t="n">
-        <v>39.09179863022437</v>
+        <v>37.89724299204907</v>
       </c>
       <c r="D14" t="n">
-        <v>1.491802575865488</v>
+        <v>1.412401644265797</v>
       </c>
       <c r="E14" t="n">
-        <v>11.93935424420693</v>
+        <v>11.77130977327281</v>
       </c>
       <c r="F14" t="n">
-        <v>0.75545641158573</v>
+        <v>0.7554679829703028</v>
       </c>
       <c r="G14" t="n">
-        <v>24.95015473976714</v>
+        <v>24.00026614114629</v>
       </c>
       <c r="H14" t="n">
-        <v>36.64988507118242</v>
+        <v>36.92812741584282</v>
       </c>
       <c r="I14" t="n">
-        <v>2.87769670835202</v>
+        <v>2.750829008019918</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721602572410813</v>
+        <v>4.721674893564393</v>
       </c>
       <c r="K14" t="n">
-        <v>16.61404767662948</v>
+        <v>17.65992314091769</v>
       </c>
       <c r="L14" t="n">
-        <v>44.19834068824677</v>
+        <v>44.35124156438871</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90418699510062</v>
+        <v>99.90840769735546</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.55379351681981</v>
+        <v>81.48885251211513</v>
       </c>
       <c r="C15" t="n">
-        <v>38.70023464523825</v>
+        <v>37.46733035457626</v>
       </c>
       <c r="D15" t="n">
-        <v>1.460399582444375</v>
+        <v>1.381235263529091</v>
       </c>
       <c r="E15" t="n">
-        <v>12.09215246958301</v>
+        <v>11.89445628072057</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7561886215297513</v>
+        <v>0.7561779325250484</v>
       </c>
       <c r="G15" t="n">
-        <v>24.42900334509913</v>
+        <v>23.47067072799024</v>
       </c>
       <c r="H15" t="n">
-        <v>36.68946573506727</v>
+        <v>36.96283055112776</v>
       </c>
       <c r="I15" t="n">
-        <v>2.40040487853533</v>
+        <v>2.297369677940865</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726178884560946</v>
+        <v>4.726112078281552</v>
       </c>
       <c r="K15" t="n">
-        <v>17.4462064831802</v>
+        <v>18.51114748788488</v>
       </c>
       <c r="L15" t="n">
-        <v>43.77362285190512</v>
+        <v>43.94501506566365</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92006398032356</v>
+        <v>99.9234929081248</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.08334322880721</v>
+        <v>78.87179783942734</v>
       </c>
       <c r="C16" t="n">
-        <v>36.60068329710691</v>
+        <v>35.20456465401341</v>
       </c>
       <c r="D16" t="n">
-        <v>1.36654799471963</v>
+        <v>1.283903303539392</v>
       </c>
       <c r="E16" t="n">
-        <v>11.64872588038457</v>
+        <v>11.37562321512443</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568187537545876</v>
+        <v>0.7567902577859378</v>
       </c>
       <c r="G16" t="n">
-        <v>22.85909002957133</v>
+        <v>21.81675524773285</v>
       </c>
       <c r="H16" t="n">
-        <v>36.72003907882497</v>
+        <v>36.99276170077776</v>
       </c>
       <c r="I16" t="n">
-        <v>2.00200428058595</v>
+        <v>1.916025003304885</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730117210966173</v>
+        <v>4.729939111162111</v>
       </c>
       <c r="K16" t="n">
-        <v>19.91665677119279</v>
+        <v>21.12820216057265</v>
       </c>
       <c r="L16" t="n">
-        <v>43.41598201840765</v>
+        <v>43.6034173610267</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93332208670735</v>
+        <v>99.93618417561277</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.87471862979228</v>
+        <v>80.74393180656377</v>
       </c>
       <c r="C17" t="n">
-        <v>37.90241269249727</v>
+        <v>36.56287861143367</v>
       </c>
       <c r="D17" t="n">
-        <v>1.367653717485882</v>
+        <v>1.284904698073367</v>
       </c>
       <c r="E17" t="n">
-        <v>12.4598999902925</v>
+        <v>12.20736044924089</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7574311228255507</v>
+        <v>0.7573805246895456</v>
       </c>
       <c r="G17" t="n">
-        <v>23.34809605706242</v>
+        <v>22.34175055963299</v>
       </c>
       <c r="H17" t="n">
-        <v>37.220260495007</v>
+        <v>37.52959370619504</v>
       </c>
       <c r="I17" t="n">
-        <v>1.987432729459246</v>
+        <v>1.889313589422277</v>
       </c>
       <c r="J17" t="n">
-        <v>4.733944517659692</v>
+        <v>4.73362827930966</v>
       </c>
       <c r="K17" t="n">
-        <v>18.12528137020772</v>
+        <v>19.25606819343623</v>
       </c>
       <c r="L17" t="n">
-        <v>43.90611173973465</v>
+        <v>44.11812515689975</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93380580243964</v>
+        <v>99.93707196176966</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.4715671469058</v>
+        <v>78.35382775066675</v>
       </c>
       <c r="C18" t="n">
-        <v>35.80596172831589</v>
+        <v>34.4636968409373</v>
       </c>
       <c r="D18" t="n">
-        <v>1.280133528714707</v>
+        <v>1.200006200769129</v>
       </c>
       <c r="E18" t="n">
-        <v>11.9387785067423</v>
+        <v>11.66335466449759</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7579576528023867</v>
+        <v>0.7578881537178718</v>
       </c>
       <c r="G18" t="n">
-        <v>21.85398263621931</v>
+        <v>20.86554687503051</v>
       </c>
       <c r="H18" t="n">
-        <v>37.24613424419117</v>
+        <v>37.55474765532037</v>
       </c>
       <c r="I18" t="n">
-        <v>1.657345248221026</v>
+        <v>1.575483240594585</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737235330014918</v>
+        <v>4.736800960736699</v>
       </c>
       <c r="K18" t="n">
-        <v>20.52843285309419</v>
+        <v>21.64617224933327</v>
       </c>
       <c r="L18" t="n">
-        <v>43.61039895388274</v>
+        <v>43.83764997668994</v>
       </c>
       <c r="M18" t="n">
-        <v>99.9447935352928</v>
+        <v>99.9475190669605</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.55288691517981</v>
+        <v>77.4026811223613</v>
       </c>
       <c r="C19" t="n">
-        <v>35.1423589327834</v>
+        <v>33.7341938377816</v>
       </c>
       <c r="D19" t="n">
-        <v>1.2473334335627</v>
+        <v>1.165997848693074</v>
       </c>
       <c r="E19" t="n">
-        <v>11.86320015568609</v>
+        <v>11.55502787863979</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7584021283557478</v>
+        <v>0.7583233160620826</v>
       </c>
       <c r="G19" t="n">
-        <v>21.2940311203505</v>
+        <v>20.27421421030706</v>
       </c>
       <c r="H19" t="n">
-        <v>37.26797582870125</v>
+        <v>37.57631074737527</v>
       </c>
       <c r="I19" t="n">
-        <v>1.381930946300084</v>
+        <v>1.333286395895998</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740013302223424</v>
+        <v>4.739520725388016</v>
       </c>
       <c r="K19" t="n">
-        <v>21.44711308482018</v>
+        <v>22.5973188776387</v>
       </c>
       <c r="L19" t="n">
-        <v>43.36449061439028</v>
+        <v>43.62406990817576</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95396263199387</v>
+        <v>99.95558262359606</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.93492903460415</v>
+        <v>74.77946107409086</v>
       </c>
       <c r="C20" t="n">
-        <v>32.73694381103216</v>
+        <v>31.31552187152824</v>
       </c>
       <c r="D20" t="n">
-        <v>1.153002550634173</v>
+        <v>1.073829371140605</v>
       </c>
       <c r="E20" t="n">
-        <v>11.15806528625702</v>
+        <v>10.8269095442119</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7587857131609516</v>
+        <v>0.7586990740054406</v>
       </c>
       <c r="G20" t="n">
-        <v>19.68364796004917</v>
+        <v>18.67160108419269</v>
       </c>
       <c r="H20" t="n">
-        <v>37.28682523420014</v>
+        <v>37.59493024244597</v>
       </c>
       <c r="I20" t="n">
-        <v>1.152191583046769</v>
+        <v>1.111622545560248</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742410707255948</v>
+        <v>4.741869212534004</v>
       </c>
       <c r="K20" t="n">
-        <v>24.06507096539585</v>
+        <v>25.22053892590914</v>
       </c>
       <c r="L20" t="n">
-        <v>43.15959825284141</v>
+        <v>43.42690346934329</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96161302926942</v>
+        <v>99.96296426678067</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.95260067517016</v>
+        <v>80.94226447777571</v>
       </c>
       <c r="C21" t="n">
-        <v>36.50511983161238</v>
+        <v>35.25572188718739</v>
       </c>
       <c r="D21" t="n">
-        <v>1.153764483392659</v>
+        <v>1.074475588431129</v>
       </c>
       <c r="E21" t="n">
-        <v>13.17787834671232</v>
+        <v>12.91872250948563</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7592871376297964</v>
+        <v>0.7591556497642191</v>
       </c>
       <c r="G21" t="n">
-        <v>21.43831335487671</v>
+        <v>20.52458459873701</v>
       </c>
       <c r="H21" t="n">
-        <v>39.05312324632869</v>
+        <v>39.45930158342249</v>
       </c>
       <c r="I21" t="n">
-        <v>1.624689496043771</v>
+        <v>1.461301736908866</v>
       </c>
       <c r="J21" t="n">
-        <v>4.745544610186228</v>
+        <v>4.74472281102637</v>
       </c>
       <c r="K21" t="n">
-        <v>18.04739932482982</v>
+        <v>19.0577355222243</v>
       </c>
       <c r="L21" t="n">
-        <v>45.39336029122988</v>
+        <v>45.63786182817462</v>
       </c>
       <c r="M21" t="n">
-        <v>99.9458794476721</v>
+        <v>99.9513192375863</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_71_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_71_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.27324151277522</v>
+        <v>45.23427905429591</v>
       </c>
       <c r="M2" t="n">
-        <v>99.15023831473638</v>
+        <v>99.63575275833128</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.04405220693907</v>
+        <v>87.95933719753961</v>
       </c>
       <c r="C3" t="n">
-        <v>45.92866480198004</v>
+        <v>45.85328505424027</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228773572864342</v>
+        <v>2.228613352958031</v>
       </c>
       <c r="E3" t="n">
-        <v>5.707279550009739</v>
+        <v>5.659738684583639</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429245242881142</v>
+        <v>0.742871117652677</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97293666433689</v>
+        <v>33.94762824016848</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17452811725325</v>
+        <v>34.17207141202314</v>
       </c>
       <c r="I3" t="n">
-        <v>6.574331501386028</v>
+        <v>6.565469904824424</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643278276800713</v>
+        <v>4.642944485329231</v>
       </c>
       <c r="K3" t="n">
-        <v>11.95594779306093</v>
+        <v>12.04066280246038</v>
       </c>
       <c r="L3" t="n">
-        <v>48.87940716608938</v>
+        <v>48.8703730419026</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7640197611303</v>
+        <v>106.7643208986032</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>86.99870552726782</v>
+        <v>86.95122235055578</v>
       </c>
       <c r="C4" t="n">
-        <v>42.51966922924255</v>
+        <v>42.4826073684935</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1777520548744</v>
+        <v>2.179482130371035</v>
       </c>
       <c r="E4" t="n">
-        <v>6.49164973169154</v>
+        <v>6.448753511111925</v>
       </c>
       <c r="F4" t="n">
-        <v>0.744487288995282</v>
+        <v>0.744432513267465</v>
       </c>
       <c r="G4" t="n">
-        <v>33.19522159256179</v>
+        <v>33.19923082203648</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24641529378297</v>
+        <v>34.24389561030338</v>
       </c>
       <c r="I4" t="n">
-        <v>5.490134009141311</v>
+        <v>5.482724555543833</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653045556220512</v>
+        <v>4.652703207921656</v>
       </c>
       <c r="K4" t="n">
-        <v>13.00129447273219</v>
+        <v>13.04877764944422</v>
       </c>
       <c r="L4" t="n">
-        <v>44.29641597854231</v>
+        <v>44.28624081803939</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81737968051706</v>
+        <v>99.81762583597711</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.85258863419318</v>
+        <v>85.81783206096897</v>
       </c>
       <c r="C5" t="n">
-        <v>42.22551238742913</v>
+        <v>42.19999820880339</v>
       </c>
       <c r="D5" t="n">
-        <v>2.121901530784802</v>
+        <v>2.124194883941965</v>
       </c>
       <c r="E5" t="n">
-        <v>7.089040713994239</v>
+        <v>7.048010337357199</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458121077865926</v>
+        <v>0.7457559803163191</v>
       </c>
       <c r="G5" t="n">
-        <v>32.34389854177407</v>
+        <v>32.35706101016423</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30735695818326</v>
+        <v>34.30477509455067</v>
       </c>
       <c r="I5" t="n">
-        <v>4.583253108004022</v>
+        <v>4.577059877661584</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661325673666203</v>
+        <v>4.660974876976994</v>
       </c>
       <c r="K5" t="n">
-        <v>14.14741136580681</v>
+        <v>14.18216793903104</v>
       </c>
       <c r="L5" t="n">
-        <v>43.47457252428791</v>
+        <v>43.4655359478449</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84749627752385</v>
+        <v>99.84770209567932</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.42243948925942</v>
+        <v>84.51430908561792</v>
       </c>
       <c r="C6" t="n">
-        <v>41.50706668107317</v>
+        <v>41.607201997215</v>
       </c>
       <c r="D6" t="n">
-        <v>2.051968737961364</v>
+        <v>2.060620463640098</v>
       </c>
       <c r="E6" t="n">
-        <v>7.492927254404268</v>
+        <v>7.473732986544898</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469385224661796</v>
+        <v>0.7468795614099826</v>
       </c>
       <c r="G6" t="n">
-        <v>31.27792110455172</v>
+        <v>31.38865579840894</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35917203344426</v>
+        <v>34.35645982485919</v>
       </c>
       <c r="I6" t="n">
-        <v>3.825146071018005</v>
+        <v>3.8199631919424</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668365765413622</v>
+        <v>4.667997258812391</v>
       </c>
       <c r="K6" t="n">
-        <v>15.57756051074058</v>
+        <v>15.48569091438209</v>
       </c>
       <c r="L6" t="n">
-        <v>42.78806022185281</v>
+        <v>42.77996653624565</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87268741366655</v>
+        <v>99.87285944784274</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.74408379125718</v>
+        <v>82.94422040490116</v>
       </c>
       <c r="C7" t="n">
-        <v>40.42267020902269</v>
+        <v>40.63035057261251</v>
       </c>
       <c r="D7" t="n">
-        <v>1.970135692287126</v>
+        <v>1.984099107793394</v>
       </c>
       <c r="E7" t="n">
-        <v>7.726060755661696</v>
+        <v>7.727425175576117</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478989209784824</v>
+        <v>0.7478362642630632</v>
       </c>
       <c r="G7" t="n">
-        <v>30.03054949552469</v>
+        <v>30.22303479139595</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40335036501019</v>
+        <v>34.4004681561009</v>
       </c>
       <c r="I7" t="n">
-        <v>3.191720305679487</v>
+        <v>3.187380258127596</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674368256115515</v>
+        <v>4.673976651644145</v>
       </c>
       <c r="K7" t="n">
-        <v>17.25591620874281</v>
+        <v>17.05577959509884</v>
       </c>
       <c r="L7" t="n">
-        <v>42.21515952470622</v>
+        <v>42.20775974362358</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89374594247172</v>
+        <v>99.89388991133492</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.4002970753122</v>
+        <v>87.68894393329494</v>
       </c>
       <c r="C8" t="n">
-        <v>42.62618197268739</v>
+        <v>42.83132427787686</v>
       </c>
       <c r="D8" t="n">
-        <v>1.974286530339255</v>
+        <v>1.988329182875994</v>
       </c>
       <c r="E8" t="n">
-        <v>9.486621848083969</v>
+        <v>9.491159834908977</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494746537122721</v>
+        <v>0.7494306420513993</v>
       </c>
       <c r="G8" t="n">
-        <v>30.5056071597735</v>
+        <v>30.69372047866002</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47583407076451</v>
+        <v>34.47380953436436</v>
       </c>
       <c r="I8" t="n">
-        <v>5.524256226936978</v>
+        <v>5.608552747612946</v>
       </c>
       <c r="J8" t="n">
-        <v>4.6842165857017</v>
+        <v>4.683941512821246</v>
       </c>
       <c r="K8" t="n">
-        <v>12.59970292468783</v>
+        <v>12.31105606670506</v>
       </c>
       <c r="L8" t="n">
-        <v>44.59036037741513</v>
+        <v>44.6710656280738</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81624527479033</v>
+        <v>99.81344597265571</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.02069588882368</v>
+        <v>85.65672399436961</v>
       </c>
       <c r="C9" t="n">
-        <v>41.10364681471729</v>
+        <v>41.66938585896173</v>
       </c>
       <c r="D9" t="n">
-        <v>1.865707155685818</v>
+        <v>1.895965041833105</v>
       </c>
       <c r="E9" t="n">
-        <v>9.73353344074547</v>
+        <v>9.830650654130013</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508298061871546</v>
+        <v>0.750796196153242</v>
       </c>
       <c r="G9" t="n">
-        <v>28.82789741606044</v>
+        <v>29.26790067385219</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53817108460911</v>
+        <v>34.53662502304913</v>
       </c>
       <c r="I9" t="n">
-        <v>4.611870696865965</v>
+        <v>4.682310179394173</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692686288669716</v>
+        <v>4.692476225957763</v>
       </c>
       <c r="K9" t="n">
-        <v>14.97930411117633</v>
+        <v>14.34327600563041</v>
       </c>
       <c r="L9" t="n">
-        <v>43.76359751224702</v>
+        <v>43.83154500352973</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84654843814064</v>
+        <v>99.84420686812186</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>82.49253334311905</v>
+        <v>83.49712777359939</v>
       </c>
       <c r="C10" t="n">
-        <v>39.29034286976118</v>
+        <v>40.23603720344754</v>
       </c>
       <c r="D10" t="n">
-        <v>1.751753184182062</v>
+        <v>1.798887509694436</v>
       </c>
       <c r="E10" t="n">
-        <v>9.78056094131434</v>
+        <v>9.978635416833759</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519976276460941</v>
+        <v>0.7519675422593826</v>
       </c>
       <c r="G10" t="n">
-        <v>27.06714231006665</v>
+        <v>27.76932052832894</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59189087172033</v>
+        <v>34.59050694393159</v>
       </c>
       <c r="I10" t="n">
-        <v>3.84920323540147</v>
+        <v>3.908012693430143</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699985172788089</v>
+        <v>4.699797139121141</v>
       </c>
       <c r="K10" t="n">
-        <v>17.50746665688097</v>
+        <v>16.50287222640061</v>
       </c>
       <c r="L10" t="n">
-        <v>43.07408295400046</v>
+        <v>43.13102639850203</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87189248064261</v>
+        <v>99.86993582835018</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>79.84833466588474</v>
+        <v>81.23430695001073</v>
       </c>
       <c r="C11" t="n">
-        <v>37.24186694644727</v>
+        <v>38.57876971428204</v>
       </c>
       <c r="D11" t="n">
-        <v>1.633939878853583</v>
+        <v>1.698226813533731</v>
       </c>
       <c r="E11" t="n">
-        <v>9.658102490689224</v>
+        <v>9.963764830000105</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530059534665693</v>
+        <v>0.7529737643085048</v>
       </c>
       <c r="G11" t="n">
-        <v>25.24675486613902</v>
+        <v>26.21542729085454</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63827385946219</v>
+        <v>34.63679315819121</v>
       </c>
       <c r="I11" t="n">
-        <v>3.211970408108088</v>
+        <v>3.261035066194483</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706287209166058</v>
+        <v>4.706086026928155</v>
       </c>
       <c r="K11" t="n">
-        <v>20.15166533411526</v>
+        <v>18.76569304998928</v>
       </c>
       <c r="L11" t="n">
-        <v>42.49954540734298</v>
+        <v>42.54698132757785</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89307768790552</v>
+        <v>99.89144409184917</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>77.28944741642094</v>
+        <v>78.7494293745262</v>
       </c>
       <c r="C12" t="n">
-        <v>35.17902294081074</v>
+        <v>36.59843666018384</v>
       </c>
       <c r="D12" t="n">
-        <v>1.521267824119819</v>
+        <v>1.588645199150543</v>
       </c>
       <c r="E12" t="n">
-        <v>9.438728556726955</v>
+        <v>9.774275323649379</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538762131667434</v>
+        <v>0.7538408963756962</v>
       </c>
       <c r="G12" t="n">
-        <v>23.50580724441662</v>
+        <v>24.52382236424333</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67830580567019</v>
+        <v>34.67668123328201</v>
       </c>
       <c r="I12" t="n">
-        <v>2.679735440028483</v>
+        <v>2.720658755477151</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711726332292146</v>
+        <v>4.711505602348101</v>
       </c>
       <c r="K12" t="n">
-        <v>22.71055258357905</v>
+        <v>21.25057062547378</v>
       </c>
       <c r="L12" t="n">
-        <v>42.02120307538498</v>
+        <v>42.0604084069481</v>
       </c>
       <c r="M12" t="n">
-        <v>99.91077859977477</v>
+        <v>99.90941569260571</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>74.75555557727031</v>
+        <v>76.37786874148165</v>
       </c>
       <c r="C13" t="n">
-        <v>33.05797347706122</v>
+        <v>34.64689242196842</v>
       </c>
       <c r="D13" t="n">
-        <v>1.410830536686209</v>
+        <v>1.485129731105998</v>
       </c>
       <c r="E13" t="n">
-        <v>9.126075232048576</v>
+        <v>9.515631095445537</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546276260654521</v>
+        <v>0.7545875405253449</v>
       </c>
       <c r="G13" t="n">
-        <v>21.79939003776029</v>
+        <v>22.92586018135105</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71287079901079</v>
+        <v>34.71102686416586</v>
       </c>
       <c r="I13" t="n">
-        <v>2.235338682789911</v>
+        <v>2.269461200604475</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716422662909076</v>
+        <v>4.716172128283406</v>
       </c>
       <c r="K13" t="n">
-        <v>25.2444444227297</v>
+        <v>23.62213125851835</v>
       </c>
       <c r="L13" t="n">
-        <v>41.62314500465274</v>
+        <v>41.6554024651944</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92556290444365</v>
+        <v>99.92442614568117</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.34007685908233</v>
+        <v>83.23691320438881</v>
       </c>
       <c r="C14" t="n">
-        <v>37.89724299204907</v>
+        <v>38.94566932812673</v>
       </c>
       <c r="D14" t="n">
-        <v>1.412401644265797</v>
+        <v>1.486841933814628</v>
       </c>
       <c r="E14" t="n">
-        <v>11.77130977327281</v>
+        <v>11.90119940098067</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554679829703028</v>
+        <v>0.7554575027944485</v>
       </c>
       <c r="G14" t="n">
-        <v>24.00026614114629</v>
+        <v>24.84707086463653</v>
       </c>
       <c r="H14" t="n">
-        <v>36.92812741584282</v>
+        <v>36.64582463946986</v>
       </c>
       <c r="I14" t="n">
-        <v>2.750829008019918</v>
+        <v>2.87890947022738</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721674893564393</v>
+        <v>4.721609392465303</v>
       </c>
       <c r="K14" t="n">
-        <v>17.65992314091769</v>
+        <v>16.76308679561118</v>
       </c>
       <c r="L14" t="n">
-        <v>44.35124156438871</v>
+        <v>44.19539073612304</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90840769735546</v>
+        <v>99.90414685986094</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>81.48885251211513</v>
+        <v>82.45777859134446</v>
       </c>
       <c r="C15" t="n">
-        <v>37.46733035457626</v>
+        <v>38.61128362671351</v>
       </c>
       <c r="D15" t="n">
-        <v>1.381235263529091</v>
+        <v>1.457957831785335</v>
       </c>
       <c r="E15" t="n">
-        <v>11.89445628072057</v>
+        <v>12.07023771087895</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7561779325250484</v>
+        <v>0.7561908764584301</v>
       </c>
       <c r="G15" t="n">
-        <v>23.47067072799024</v>
+        <v>24.36437979058138</v>
       </c>
       <c r="H15" t="n">
-        <v>36.96283055112776</v>
+        <v>36.68139921856407</v>
       </c>
       <c r="I15" t="n">
-        <v>2.297369677940865</v>
+        <v>2.401420185211106</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726112078281552</v>
+        <v>4.726192977865188</v>
       </c>
       <c r="K15" t="n">
-        <v>18.51114748788488</v>
+        <v>17.54222140865554</v>
       </c>
       <c r="L15" t="n">
-        <v>43.94501506566365</v>
+        <v>43.76652525712465</v>
       </c>
       <c r="M15" t="n">
-        <v>99.9234929081248</v>
+        <v>99.92003029249369</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>78.87179783942734</v>
+        <v>80.03830064413636</v>
       </c>
       <c r="C16" t="n">
-        <v>35.20456465401341</v>
+        <v>36.56281884377533</v>
       </c>
       <c r="D16" t="n">
-        <v>1.283903303539392</v>
+        <v>1.366004265584488</v>
       </c>
       <c r="E16" t="n">
-        <v>11.37562321512443</v>
+        <v>11.64277523291344</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7567902577859378</v>
+        <v>0.7568216323763838</v>
       </c>
       <c r="G16" t="n">
-        <v>21.81675524773285</v>
+        <v>22.82771558728796</v>
       </c>
       <c r="H16" t="n">
-        <v>36.99276170077776</v>
+        <v>36.71199600352436</v>
       </c>
       <c r="I16" t="n">
-        <v>1.916025003304885</v>
+        <v>2.002852720097337</v>
       </c>
       <c r="J16" t="n">
-        <v>4.729939111162111</v>
+        <v>4.730135202352399</v>
       </c>
       <c r="K16" t="n">
-        <v>21.12820216057265</v>
+        <v>19.96169935586363</v>
       </c>
       <c r="L16" t="n">
-        <v>43.6034173610267</v>
+        <v>43.40877568410518</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93618417561277</v>
+        <v>99.93329388374414</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>80.74393180656377</v>
+        <v>81.69831820229321</v>
       </c>
       <c r="C17" t="n">
-        <v>36.56287861143367</v>
+        <v>37.77944507241408</v>
       </c>
       <c r="D17" t="n">
-        <v>1.284904698073367</v>
+        <v>1.367110258061123</v>
       </c>
       <c r="E17" t="n">
-        <v>12.20736044924089</v>
+        <v>12.4111148945885</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7573805246895456</v>
+        <v>0.7574343969574703</v>
       </c>
       <c r="G17" t="n">
-        <v>22.34175055963299</v>
+        <v>23.27437384751012</v>
       </c>
       <c r="H17" t="n">
-        <v>37.52959370619504</v>
+        <v>37.16989574378485</v>
       </c>
       <c r="I17" t="n">
-        <v>1.889313589422277</v>
+        <v>1.984424080406979</v>
       </c>
       <c r="J17" t="n">
-        <v>4.73362827930966</v>
+        <v>4.733964980984189</v>
       </c>
       <c r="K17" t="n">
-        <v>19.25606819343623</v>
+        <v>18.30168179770678</v>
       </c>
       <c r="L17" t="n">
-        <v>44.11812515689975</v>
+        <v>43.85277917384838</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93707196176966</v>
+        <v>99.93390604396924</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.35382775066675</v>
+        <v>79.42607295829102</v>
       </c>
       <c r="C18" t="n">
-        <v>34.4636968409373</v>
+        <v>35.81340260872709</v>
       </c>
       <c r="D18" t="n">
-        <v>1.200006200769129</v>
+        <v>1.284163649263281</v>
       </c>
       <c r="E18" t="n">
-        <v>11.66335466449759</v>
+        <v>11.93390184226766</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7578881537178718</v>
+        <v>0.7579604329159729</v>
       </c>
       <c r="G18" t="n">
-        <v>20.86554687503051</v>
+        <v>21.86224898694321</v>
       </c>
       <c r="H18" t="n">
-        <v>37.55474765532037</v>
+        <v>37.19571012693614</v>
       </c>
       <c r="I18" t="n">
-        <v>1.575483240594585</v>
+        <v>1.654835214239915</v>
       </c>
       <c r="J18" t="n">
-        <v>4.736800960736699</v>
+        <v>4.737252705724831</v>
       </c>
       <c r="K18" t="n">
-        <v>21.64617224933327</v>
+        <v>20.57392704170899</v>
       </c>
       <c r="L18" t="n">
-        <v>43.83764997668994</v>
+        <v>43.55754745844152</v>
       </c>
       <c r="M18" t="n">
-        <v>99.9475190669605</v>
+        <v>99.94487710887759</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.4026811223613</v>
+        <v>78.53958423378728</v>
       </c>
       <c r="C19" t="n">
-        <v>33.7341938377816</v>
+        <v>35.18162441108637</v>
       </c>
       <c r="D19" t="n">
-        <v>1.165997848693074</v>
+        <v>1.252445529157543</v>
       </c>
       <c r="E19" t="n">
-        <v>11.55502787863979</v>
+        <v>11.86911399937819</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7583233160620826</v>
+        <v>0.7584043117623958</v>
       </c>
       <c r="G19" t="n">
-        <v>20.27421421030706</v>
+        <v>21.32226372918636</v>
       </c>
       <c r="H19" t="n">
-        <v>37.57631074737527</v>
+        <v>37.21749277967898</v>
       </c>
       <c r="I19" t="n">
-        <v>1.333286395895998</v>
+        <v>1.379836936108831</v>
       </c>
       <c r="J19" t="n">
-        <v>4.739520725388016</v>
+        <v>4.740026948514974</v>
       </c>
       <c r="K19" t="n">
-        <v>22.5973188776387</v>
+        <v>21.46041576621273</v>
       </c>
       <c r="L19" t="n">
-        <v>43.62406990817576</v>
+        <v>43.3119921778609</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95558262359606</v>
+        <v>99.95403235516</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>74.77946107409086</v>
+        <v>76.119831397222</v>
       </c>
       <c r="C20" t="n">
-        <v>31.31552187152824</v>
+        <v>32.97411875182321</v>
       </c>
       <c r="D20" t="n">
-        <v>1.073829371140605</v>
+        <v>1.165045168785362</v>
       </c>
       <c r="E20" t="n">
-        <v>10.8269095442119</v>
+        <v>11.23258314273303</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7586990740054406</v>
+        <v>0.7587863853159031</v>
       </c>
       <c r="G20" t="n">
-        <v>18.67160108419269</v>
+        <v>19.83431595780894</v>
       </c>
       <c r="H20" t="n">
-        <v>37.59493024244597</v>
+        <v>37.23624243536847</v>
       </c>
       <c r="I20" t="n">
-        <v>1.111622545560248</v>
+        <v>1.1504433989859</v>
       </c>
       <c r="J20" t="n">
-        <v>4.741869212534004</v>
+        <v>4.742414908224394</v>
       </c>
       <c r="K20" t="n">
-        <v>25.22053892590914</v>
+        <v>23.88016860277801</v>
       </c>
       <c r="L20" t="n">
-        <v>43.42690346934329</v>
+        <v>43.10738384161797</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96296426678067</v>
+        <v>99.9616711962192</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>80.94226447777571</v>
+        <v>81.88786423155214</v>
       </c>
       <c r="C21" t="n">
-        <v>35.25572188718739</v>
+        <v>36.57716219560662</v>
       </c>
       <c r="D21" t="n">
-        <v>1.074475588431129</v>
+        <v>1.16581386572551</v>
       </c>
       <c r="E21" t="n">
-        <v>12.91872250948563</v>
+        <v>13.16946739313918</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7591556497642191</v>
+        <v>0.7592870326626721</v>
       </c>
       <c r="G21" t="n">
-        <v>20.52458459873701</v>
+        <v>21.50672752002171</v>
       </c>
       <c r="H21" t="n">
-        <v>39.45930158342249</v>
+        <v>38.92013579072916</v>
       </c>
       <c r="I21" t="n">
-        <v>1.461301736908866</v>
+        <v>1.620888675132225</v>
       </c>
       <c r="J21" t="n">
-        <v>4.74472281102637</v>
+        <v>4.7455439541417</v>
       </c>
       <c r="K21" t="n">
-        <v>19.0577355222243</v>
+        <v>18.11213576844785</v>
       </c>
       <c r="L21" t="n">
-        <v>45.63786182817462</v>
+        <v>45.2567080386869</v>
       </c>
       <c r="M21" t="n">
-        <v>99.9513192375863</v>
+        <v>99.94600600274137</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_71_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_71_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.23427905429591</v>
+        <v>43.57218024221879</v>
       </c>
       <c r="M2" t="n">
-        <v>99.63575275833128</v>
+        <v>94.44069515471156</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.95933719753961</v>
+        <v>81.40462406279329</v>
       </c>
       <c r="C3" t="n">
-        <v>45.85328505424027</v>
+        <v>43.16017961834884</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228613352958031</v>
+        <v>2.176541300557769</v>
       </c>
       <c r="E3" t="n">
-        <v>5.659738684583639</v>
+        <v>4.139778504420089</v>
       </c>
       <c r="F3" t="n">
-        <v>0.742871117652677</v>
+        <v>0.7375819250262813</v>
       </c>
       <c r="G3" t="n">
-        <v>33.94762824016848</v>
+        <v>32.73880872922312</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17207141202314</v>
+        <v>33.92876855120893</v>
       </c>
       <c r="I3" t="n">
-        <v>6.565469904824424</v>
+        <v>3.073258020942839</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642944485329231</v>
+        <v>4.609887031414257</v>
       </c>
       <c r="K3" t="n">
-        <v>12.04066280246038</v>
+        <v>18.59537593720672</v>
       </c>
       <c r="L3" t="n">
-        <v>48.8703730419026</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7643208986032</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>86.95122235055578</v>
+        <v>88.26150407720294</v>
       </c>
       <c r="C4" t="n">
-        <v>42.4826073684935</v>
+        <v>42.68175396468231</v>
       </c>
       <c r="D4" t="n">
-        <v>2.179482130371035</v>
+        <v>2.182156861220026</v>
       </c>
       <c r="E4" t="n">
-        <v>6.448753511111925</v>
+        <v>6.460987677753517</v>
       </c>
       <c r="F4" t="n">
-        <v>0.744432513267465</v>
+        <v>0.7394849148947978</v>
       </c>
       <c r="G4" t="n">
-        <v>33.19923082203648</v>
+        <v>33.40924508536902</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24389561030338</v>
+        <v>34.01630608516069</v>
       </c>
       <c r="I4" t="n">
-        <v>5.482724555543833</v>
+        <v>6.831542734712414</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652703207921656</v>
+        <v>4.621780718092485</v>
       </c>
       <c r="K4" t="n">
-        <v>13.04877764944422</v>
+        <v>11.73849592279705</v>
       </c>
       <c r="L4" t="n">
-        <v>44.28624081803939</v>
+        <v>45.35261803091105</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81762583597711</v>
+        <v>99.7728679183904</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.81783206096897</v>
+        <v>86.78963059774716</v>
       </c>
       <c r="C5" t="n">
-        <v>42.19999820880339</v>
+        <v>42.26882643960273</v>
       </c>
       <c r="D5" t="n">
-        <v>2.124194883941965</v>
+        <v>2.110393668370392</v>
       </c>
       <c r="E5" t="n">
-        <v>7.048010337357199</v>
+        <v>7.199413848319977</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457559803163191</v>
+        <v>0.741105337862015</v>
       </c>
       <c r="G5" t="n">
-        <v>32.35706101016423</v>
+        <v>32.31053667414987</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30477509455067</v>
+        <v>34.09084554165268</v>
       </c>
       <c r="I5" t="n">
-        <v>4.577059877661584</v>
+        <v>5.705427165754632</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660974876976994</v>
+        <v>4.631908361637593</v>
       </c>
       <c r="K5" t="n">
-        <v>14.18216793903104</v>
+        <v>13.21036940225285</v>
       </c>
       <c r="L5" t="n">
-        <v>43.4655359478449</v>
+        <v>44.33103908218019</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84770209567932</v>
+        <v>99.81023492403577</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.51430908561792</v>
+        <v>85.04384215078579</v>
       </c>
       <c r="C6" t="n">
-        <v>41.607201997215</v>
+        <v>41.40808152142901</v>
       </c>
       <c r="D6" t="n">
-        <v>2.060620463640098</v>
+        <v>2.025646943653557</v>
       </c>
       <c r="E6" t="n">
-        <v>7.473732986544898</v>
+        <v>7.704208111266937</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468795614099826</v>
+        <v>0.742489008806182</v>
       </c>
       <c r="G6" t="n">
-        <v>31.38865579840894</v>
+        <v>31.01304787003884</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35645982485919</v>
+        <v>34.15449440508436</v>
       </c>
       <c r="I6" t="n">
-        <v>3.8199631919424</v>
+        <v>4.763399506897262</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667997258812391</v>
+        <v>4.640556305038636</v>
       </c>
       <c r="K6" t="n">
-        <v>15.48569091438209</v>
+        <v>14.95615784921423</v>
       </c>
       <c r="L6" t="n">
-        <v>42.77996653624565</v>
+        <v>43.47727654141914</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87285944784274</v>
+        <v>99.84151591206238</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.94422040490116</v>
+        <v>83.03183369334484</v>
       </c>
       <c r="C7" t="n">
-        <v>40.63035057261251</v>
+        <v>40.13496674117143</v>
       </c>
       <c r="D7" t="n">
-        <v>1.984099107793394</v>
+        <v>1.92868782708369</v>
       </c>
       <c r="E7" t="n">
-        <v>7.727425175576117</v>
+        <v>7.998079611364582</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478362642630632</v>
+        <v>0.7436741020856027</v>
       </c>
       <c r="G7" t="n">
-        <v>30.22303479139595</v>
+        <v>29.5285849763253</v>
       </c>
       <c r="H7" t="n">
-        <v>34.4004681561009</v>
+        <v>34.20900869593772</v>
       </c>
       <c r="I7" t="n">
-        <v>3.187380258127596</v>
+        <v>3.97583534251294</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673976651644145</v>
+        <v>4.647963138035016</v>
       </c>
       <c r="K7" t="n">
-        <v>17.05577959509884</v>
+        <v>16.96816630665516</v>
       </c>
       <c r="L7" t="n">
-        <v>42.20775974362358</v>
+        <v>42.76455029920405</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89388991133492</v>
+        <v>99.86768334703063</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.68894393329494</v>
+        <v>80.87074698090387</v>
       </c>
       <c r="C8" t="n">
-        <v>42.83132427787686</v>
+        <v>38.590139157545</v>
       </c>
       <c r="D8" t="n">
-        <v>1.988329182875994</v>
+        <v>1.825540893907587</v>
       </c>
       <c r="E8" t="n">
-        <v>9.491159834908977</v>
+        <v>8.123293863752748</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494306420513993</v>
+        <v>0.7446910778074708</v>
       </c>
       <c r="G8" t="n">
-        <v>30.69372047866002</v>
+        <v>27.94938540936203</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47380953436436</v>
+        <v>34.25578957914365</v>
       </c>
       <c r="I8" t="n">
-        <v>5.608552747612946</v>
+        <v>3.317726920633698</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683941512821246</v>
+        <v>4.654319236296692</v>
       </c>
       <c r="K8" t="n">
-        <v>12.31105606670506</v>
+        <v>19.12925301909613</v>
       </c>
       <c r="L8" t="n">
-        <v>44.6710656280738</v>
+        <v>42.17016795273352</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81344597265571</v>
+        <v>99.88956012937464</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.65672399436961</v>
+        <v>78.52903686612505</v>
       </c>
       <c r="C9" t="n">
-        <v>41.66938585896173</v>
+        <v>36.76199653569459</v>
       </c>
       <c r="D9" t="n">
-        <v>1.895965041833105</v>
+        <v>1.714754107990329</v>
       </c>
       <c r="E9" t="n">
-        <v>9.830650654130013</v>
+        <v>8.091651518041475</v>
       </c>
       <c r="F9" t="n">
-        <v>0.750796196153242</v>
+        <v>0.7455660494712283</v>
       </c>
       <c r="G9" t="n">
-        <v>29.26790067385219</v>
+        <v>26.2532182140942</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53662502304913</v>
+        <v>34.29603827567649</v>
       </c>
       <c r="I9" t="n">
-        <v>4.682310179394173</v>
+        <v>2.768020891656141</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692476225957763</v>
+        <v>4.659787809195176</v>
       </c>
       <c r="K9" t="n">
-        <v>14.34327600563041</v>
+        <v>21.47096313387494</v>
       </c>
       <c r="L9" t="n">
-        <v>43.83154500352973</v>
+        <v>41.67488124930176</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84420686812186</v>
+        <v>99.90784091887129</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.49712777359939</v>
+        <v>84.32029143097924</v>
       </c>
       <c r="C10" t="n">
-        <v>40.23603720344754</v>
+        <v>40.71633969720747</v>
       </c>
       <c r="D10" t="n">
-        <v>1.798887509694436</v>
+        <v>1.716677534785415</v>
       </c>
       <c r="E10" t="n">
-        <v>9.978635416833759</v>
+        <v>10.29494991310773</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519675422593826</v>
+        <v>0.7464023453053525</v>
       </c>
       <c r="G10" t="n">
-        <v>27.76932052832894</v>
+        <v>28.00398111622914</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59050694393159</v>
+        <v>36.05582274862583</v>
       </c>
       <c r="I10" t="n">
-        <v>3.908012693430143</v>
+        <v>2.837443114767309</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699797139121141</v>
+        <v>4.665014658158453</v>
       </c>
       <c r="K10" t="n">
-        <v>16.50287222640061</v>
+        <v>15.67970856902074</v>
       </c>
       <c r="L10" t="n">
-        <v>43.13102639850203</v>
+        <v>43.50947626903161</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86993582835018</v>
+        <v>99.90552453525983</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.23430695001073</v>
+        <v>83.62938648411559</v>
       </c>
       <c r="C11" t="n">
-        <v>38.57876971428204</v>
+        <v>40.34704794742262</v>
       </c>
       <c r="D11" t="n">
-        <v>1.698226813533731</v>
+        <v>1.67844148965482</v>
       </c>
       <c r="E11" t="n">
-        <v>9.963764830000105</v>
+        <v>10.5253066449604</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529737643085048</v>
+        <v>0.7471247037196349</v>
       </c>
       <c r="G11" t="n">
-        <v>26.21542729085454</v>
+        <v>27.43522245367287</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63679315819121</v>
+        <v>36.14569904507541</v>
       </c>
       <c r="I11" t="n">
-        <v>3.261035066194483</v>
+        <v>2.428062748784719</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706086026928155</v>
+        <v>4.669529398247718</v>
       </c>
       <c r="K11" t="n">
-        <v>18.76569304998928</v>
+        <v>16.37061351588444</v>
       </c>
       <c r="L11" t="n">
-        <v>42.54698132757785</v>
+        <v>43.20148136424596</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89144409184917</v>
+        <v>99.919142827553</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.7494293745262</v>
+        <v>81.17086443070957</v>
       </c>
       <c r="C12" t="n">
-        <v>36.59843666018384</v>
+        <v>38.26480417593294</v>
       </c>
       <c r="D12" t="n">
-        <v>1.588645199150543</v>
+        <v>1.575648991850672</v>
       </c>
       <c r="E12" t="n">
-        <v>9.774275323649379</v>
+        <v>10.21821851692724</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538408963756962</v>
+        <v>0.7477460180109339</v>
       </c>
       <c r="G12" t="n">
-        <v>24.52382236424333</v>
+        <v>25.75501193623299</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67668123328201</v>
+        <v>36.17575806905613</v>
       </c>
       <c r="I12" t="n">
-        <v>2.720658755477151</v>
+        <v>2.025068286063266</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711505602348101</v>
+        <v>4.673412612568337</v>
       </c>
       <c r="K12" t="n">
-        <v>21.25057062547378</v>
+        <v>18.82913556929043</v>
       </c>
       <c r="L12" t="n">
-        <v>42.0604084069481</v>
+        <v>42.8386140673104</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90941569260571</v>
+        <v>99.93255381253377</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.37786874148165</v>
+        <v>82.36558266443866</v>
       </c>
       <c r="C13" t="n">
-        <v>34.64689242196842</v>
+        <v>39.25565683685512</v>
       </c>
       <c r="D13" t="n">
-        <v>1.485129731105998</v>
+        <v>1.576845514211602</v>
       </c>
       <c r="E13" t="n">
-        <v>9.515631095445537</v>
+        <v>10.86222561855572</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545875405253449</v>
+        <v>0.748313844243473</v>
       </c>
       <c r="G13" t="n">
-        <v>22.92586018135105</v>
+        <v>26.09808197075179</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71102686416586</v>
+        <v>36.5267414496501</v>
       </c>
       <c r="I13" t="n">
-        <v>2.269461200604475</v>
+        <v>1.876412740504265</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716172128283406</v>
+        <v>4.676961526521707</v>
       </c>
       <c r="K13" t="n">
-        <v>23.62213125851835</v>
+        <v>17.63441733556136</v>
       </c>
       <c r="L13" t="n">
-        <v>41.6554024651944</v>
+        <v>43.04742619744168</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92442614568117</v>
+        <v>99.93750036985816</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.23691320438881</v>
+        <v>79.95810167417645</v>
       </c>
       <c r="C14" t="n">
-        <v>38.94566932812673</v>
+        <v>37.13859883812599</v>
       </c>
       <c r="D14" t="n">
-        <v>1.486841933814628</v>
+        <v>1.479301631520316</v>
       </c>
       <c r="E14" t="n">
-        <v>11.90119940098067</v>
+        <v>10.45106971003907</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554575027944485</v>
+        <v>0.7488019684833899</v>
       </c>
       <c r="G14" t="n">
-        <v>24.84707086463653</v>
+        <v>24.48365099239727</v>
       </c>
       <c r="H14" t="n">
-        <v>36.64582463946986</v>
+        <v>36.55056780010974</v>
       </c>
       <c r="I14" t="n">
-        <v>2.87890947022738</v>
+        <v>1.56469726860547</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721609392465303</v>
+        <v>4.680012303021188</v>
       </c>
       <c r="K14" t="n">
-        <v>16.76308679561118</v>
+        <v>20.04189832582355</v>
       </c>
       <c r="L14" t="n">
-        <v>44.19539073612304</v>
+        <v>42.76738025992536</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90414685986094</v>
+        <v>99.9478774238749</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.45777859134446</v>
+        <v>78.83351949643875</v>
       </c>
       <c r="C15" t="n">
-        <v>38.61128362671351</v>
+        <v>36.21953895756377</v>
       </c>
       <c r="D15" t="n">
-        <v>1.457957831785335</v>
+        <v>1.432727655775287</v>
       </c>
       <c r="E15" t="n">
-        <v>12.07023771087895</v>
+        <v>10.34528623445809</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7561908764584301</v>
+        <v>0.7492260879332571</v>
       </c>
       <c r="G15" t="n">
-        <v>24.36437979058138</v>
+        <v>23.71281363024433</v>
       </c>
       <c r="H15" t="n">
-        <v>36.68139921856407</v>
+        <v>36.57126994481578</v>
       </c>
       <c r="I15" t="n">
-        <v>2.401420185211106</v>
+        <v>1.339532893629153</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726192977865188</v>
+        <v>4.682663049582858</v>
       </c>
       <c r="K15" t="n">
-        <v>17.54222140865554</v>
+        <v>21.16648050356124</v>
       </c>
       <c r="L15" t="n">
-        <v>43.76652525712465</v>
+        <v>42.56935471836712</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92003029249369</v>
+        <v>99.95537417949213</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.03830064413636</v>
+        <v>76.10236610556342</v>
       </c>
       <c r="C16" t="n">
-        <v>36.56281884377533</v>
+        <v>33.6949464527619</v>
       </c>
       <c r="D16" t="n">
-        <v>1.366004265584488</v>
+        <v>1.323120767046084</v>
       </c>
       <c r="E16" t="n">
-        <v>11.64277523291344</v>
+        <v>9.739985809352939</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568216323763838</v>
+        <v>0.7495925913331057</v>
       </c>
       <c r="G16" t="n">
-        <v>22.82771558728796</v>
+        <v>21.89873004321391</v>
       </c>
       <c r="H16" t="n">
-        <v>36.71199600352436</v>
+        <v>36.58915973134008</v>
       </c>
       <c r="I16" t="n">
-        <v>2.002852720097337</v>
+        <v>1.116823467445404</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730135202352399</v>
+        <v>4.684953695831911</v>
       </c>
       <c r="K16" t="n">
-        <v>19.96169935586363</v>
+        <v>23.89763389443656</v>
       </c>
       <c r="L16" t="n">
-        <v>43.40877568410518</v>
+        <v>42.37021040575627</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93329388374414</v>
+        <v>99.96279075295473</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.69831820229321</v>
+        <v>81.88292604059978</v>
       </c>
       <c r="C17" t="n">
-        <v>37.77944507241408</v>
+        <v>37.52704443824793</v>
       </c>
       <c r="D17" t="n">
-        <v>1.367110258061123</v>
+        <v>1.323786704296479</v>
       </c>
       <c r="E17" t="n">
-        <v>12.4111148945885</v>
+        <v>11.75668667724655</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7574343969574703</v>
+        <v>0.7499698672716456</v>
       </c>
       <c r="G17" t="n">
-        <v>23.27437384751012</v>
+        <v>23.71548885064384</v>
       </c>
       <c r="H17" t="n">
-        <v>37.16989574378485</v>
+        <v>38.41331234937088</v>
       </c>
       <c r="I17" t="n">
-        <v>1.984424080406979</v>
+        <v>1.236369921322603</v>
       </c>
       <c r="J17" t="n">
-        <v>4.733964980984189</v>
+        <v>4.687311670447786</v>
       </c>
       <c r="K17" t="n">
-        <v>18.30168179770678</v>
+        <v>18.11707395940022</v>
       </c>
       <c r="L17" t="n">
-        <v>43.85277917384838</v>
+        <v>44.31469000370171</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93390604396924</v>
+        <v>99.95880840134986</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.42607295829102</v>
+        <v>83.57843377826515</v>
       </c>
       <c r="C18" t="n">
-        <v>35.81340260872709</v>
+        <v>38.27684286447166</v>
       </c>
       <c r="D18" t="n">
-        <v>1.284163649263281</v>
+        <v>1.324912202193263</v>
       </c>
       <c r="E18" t="n">
-        <v>11.93390184226766</v>
+        <v>12.37280262960602</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7579604329159729</v>
+        <v>0.7506074998339954</v>
       </c>
       <c r="G18" t="n">
-        <v>21.86224898694321</v>
+        <v>23.86106392219232</v>
       </c>
       <c r="H18" t="n">
-        <v>37.19571012693614</v>
+        <v>38.44597176656958</v>
       </c>
       <c r="I18" t="n">
-        <v>1.654835214239915</v>
+        <v>2.131778883907519</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737252705724831</v>
+        <v>4.691296873962473</v>
       </c>
       <c r="K18" t="n">
-        <v>20.57392704170899</v>
+        <v>16.42156622173485</v>
       </c>
       <c r="L18" t="n">
-        <v>43.55754745844152</v>
+        <v>45.23059198172979</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94487710887759</v>
+        <v>99.9290010679363</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.53958423378728</v>
+        <v>80.49301672831238</v>
       </c>
       <c r="C19" t="n">
-        <v>35.18162441108637</v>
+        <v>35.52004960441552</v>
       </c>
       <c r="D19" t="n">
-        <v>1.252445529157543</v>
+        <v>1.216967239745348</v>
       </c>
       <c r="E19" t="n">
-        <v>11.86911399937819</v>
+        <v>11.66104801089593</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7584043117623958</v>
+        <v>0.7511601037577443</v>
       </c>
       <c r="G19" t="n">
-        <v>21.32226372918636</v>
+        <v>21.91702442675666</v>
       </c>
       <c r="H19" t="n">
-        <v>37.21749277967898</v>
+        <v>38.47427603325389</v>
       </c>
       <c r="I19" t="n">
-        <v>1.379836936108831</v>
+        <v>1.777790265416886</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740026948514974</v>
+        <v>4.694750648485903</v>
       </c>
       <c r="K19" t="n">
-        <v>21.46041576621273</v>
+        <v>19.50698327168764</v>
       </c>
       <c r="L19" t="n">
-        <v>43.3119921778609</v>
+        <v>44.91375104378832</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95403235516</v>
+        <v>99.94078391989146</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.119831397222</v>
+        <v>77.42738189460017</v>
       </c>
       <c r="C20" t="n">
-        <v>32.97411875182321</v>
+        <v>32.72748026208471</v>
       </c>
       <c r="D20" t="n">
-        <v>1.165045168785362</v>
+        <v>1.110453962124098</v>
       </c>
       <c r="E20" t="n">
-        <v>11.23258314273303</v>
+        <v>10.88750473750883</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7587863853159031</v>
+        <v>0.7516394982527319</v>
       </c>
       <c r="G20" t="n">
-        <v>19.83431595780894</v>
+        <v>19.99876892146685</v>
       </c>
       <c r="H20" t="n">
-        <v>37.23624243536847</v>
+        <v>38.49883052707845</v>
       </c>
       <c r="I20" t="n">
-        <v>1.1504433989859</v>
+        <v>1.482437384089617</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742414908224394</v>
+        <v>4.697746864079575</v>
       </c>
       <c r="K20" t="n">
-        <v>23.88016860277801</v>
+        <v>22.57261810539985</v>
       </c>
       <c r="L20" t="n">
-        <v>43.10738384161797</v>
+        <v>44.6505185695872</v>
       </c>
       <c r="M20" t="n">
-        <v>99.9616711962192</v>
+        <v>99.95061693707176</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.88786423155214</v>
+        <v>74.3841407260218</v>
       </c>
       <c r="C21" t="n">
-        <v>36.57716219560662</v>
+        <v>29.91102003189773</v>
       </c>
       <c r="D21" t="n">
-        <v>1.16581386572551</v>
+        <v>1.005394144078543</v>
       </c>
       <c r="E21" t="n">
-        <v>13.16946739313918</v>
+        <v>10.06344830874057</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7592870326626721</v>
+        <v>0.7520558338946091</v>
       </c>
       <c r="G21" t="n">
-        <v>21.50672752002171</v>
+        <v>18.1066895596125</v>
       </c>
       <c r="H21" t="n">
-        <v>38.92013579072916</v>
+        <v>38.5201551585757</v>
       </c>
       <c r="I21" t="n">
-        <v>1.620888675132225</v>
+        <v>1.236048759278562</v>
       </c>
       <c r="J21" t="n">
-        <v>4.7455439541417</v>
+        <v>4.700348961841308</v>
       </c>
       <c r="K21" t="n">
-        <v>18.11213576844785</v>
+        <v>25.6158592739782</v>
       </c>
       <c r="L21" t="n">
-        <v>45.2567080386869</v>
+        <v>44.43194187789938</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94600600274137</v>
+        <v>99.95882118377531</v>
       </c>
     </row>
   </sheetData>
